--- a/Result/profitability/1101.xlsx
+++ b/Result/profitability/1101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02250000000000001</v>
+        <v>-0.03874999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>19.1625</v>
+        <v>18.3525</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01124999999999998</v>
+        <v>-0.0175</v>
       </c>
       <c r="N3" t="n">
-        <v>17.46125</v>
+        <v>16.77375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01250000000000002</v>
+        <v>0.015</v>
       </c>
       <c r="N4" t="n">
-        <v>15.74625</v>
+        <v>15.8625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02124999999999998</v>
+        <v>0.0575</v>
       </c>
       <c r="N5" t="n">
-        <v>14.3075</v>
+        <v>14.64125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02874999999999998</v>
+        <v>0.235</v>
       </c>
       <c r="N6" t="n">
-        <v>13.63375</v>
+        <v>13.0275</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2725</v>
+        <v>0.34875</v>
       </c>
       <c r="N7" t="n">
-        <v>12.9275</v>
+        <v>12.84</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.41625</v>
+        <v>0.44</v>
       </c>
       <c r="N8" t="n">
-        <v>13.17875</v>
+        <v>13.0625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.78</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5287499999999999</v>
+        <v>0.5287500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>15.575</v>
@@ -2026,7 +2026,7 @@
         <v>0.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0.58625</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N13" t="n">
         <v>17.69875</v>
@@ -9828,6 +9828,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>38122</v>
+      </c>
+      <c r="D75" t="n">
+        <v>31338</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6783</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2378</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2124</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4502</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2562</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.6475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04967948717948711</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1765873015873016</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
